--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/86.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/86.xlsx
@@ -426,13 +426,13 @@
         <v>-9.866705387038966</v>
       </c>
       <c r="E2">
-        <v>-16.2327926469728</v>
+        <v>-15.36475663528652</v>
       </c>
       <c r="F2">
-        <v>-0.2586313610147638</v>
+        <v>-0.3414987508886179</v>
       </c>
       <c r="G2">
-        <v>-15.47648870020767</v>
+        <v>-11.38473883257974</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.496686843216224</v>
       </c>
       <c r="E3">
-        <v>-16.38225040312195</v>
+        <v>-16.67635667602412</v>
       </c>
       <c r="F3">
-        <v>-0.2330290096964395</v>
+        <v>-0.5676322830766466</v>
       </c>
       <c r="G3">
-        <v>-14.98639719384674</v>
+        <v>-12.13330614773758</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.048293804468035</v>
       </c>
       <c r="E4">
-        <v>-16.62544757122988</v>
+        <v>-17.34365449189839</v>
       </c>
       <c r="F4">
-        <v>0.05019311879032269</v>
+        <v>-0.07722552674089446</v>
       </c>
       <c r="G4">
-        <v>-14.31630470542455</v>
+        <v>-11.38402706528879</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.555694784118968</v>
       </c>
       <c r="E5">
-        <v>-16.50732685521381</v>
+        <v>-17.11357178451667</v>
       </c>
       <c r="F5">
-        <v>0.3702419769033425</v>
+        <v>-0.1961774290480979</v>
       </c>
       <c r="G5">
-        <v>-13.85394894959162</v>
+        <v>-11.97411856548172</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.014254796977784</v>
       </c>
       <c r="E6">
-        <v>-17.18206495388269</v>
+        <v>-17.85335688383173</v>
       </c>
       <c r="F6">
-        <v>0.3941354062696914</v>
+        <v>0.0990924749449803</v>
       </c>
       <c r="G6">
-        <v>-13.38800952821244</v>
+        <v>-10.80289721187067</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.427394519954577</v>
       </c>
       <c r="E7">
-        <v>-18.32640127867297</v>
+        <v>-17.96060473375538</v>
       </c>
       <c r="F7">
-        <v>0.56943368768272</v>
+        <v>0.1378120240866348</v>
       </c>
       <c r="G7">
-        <v>-13.05716022810875</v>
+        <v>-10.95558288268739</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.80620670253316</v>
       </c>
       <c r="E8">
-        <v>-18.36853872931434</v>
+        <v>-19.01657241675999</v>
       </c>
       <c r="F8">
-        <v>0.8558516576094827</v>
+        <v>0.3805576361704047</v>
       </c>
       <c r="G8">
-        <v>-12.38904248010074</v>
+        <v>-10.45405840730658</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.161904286201153</v>
       </c>
       <c r="E9">
-        <v>-19.5958683972432</v>
+        <v>-19.8164322522608</v>
       </c>
       <c r="F9">
-        <v>0.8038765732882305</v>
+        <v>0.6113689590820421</v>
       </c>
       <c r="G9">
-        <v>-12.4298151589624</v>
+        <v>-10.16937797529358</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.495253554272028</v>
       </c>
       <c r="E10">
-        <v>-19.51039797882243</v>
+        <v>-20.12281521819775</v>
       </c>
       <c r="F10">
-        <v>0.983310893143437</v>
+        <v>0.5501269286256719</v>
       </c>
       <c r="G10">
-        <v>-11.76997046425703</v>
+        <v>-9.629169775286384</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.823987690248987</v>
       </c>
       <c r="E11">
-        <v>-20.60600339481617</v>
+        <v>-20.33899098190191</v>
       </c>
       <c r="F11">
-        <v>1.308971940410423</v>
+        <v>0.8590441855798719</v>
       </c>
       <c r="G11">
-        <v>-10.46382782719297</v>
+        <v>-9.472438617820668</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.156215050301168</v>
       </c>
       <c r="E12">
-        <v>-20.69579850591427</v>
+        <v>-20.86050363404725</v>
       </c>
       <c r="F12">
-        <v>1.68185821331101</v>
+        <v>1.22438568817576</v>
       </c>
       <c r="G12">
-        <v>-10.43276166785245</v>
+        <v>-8.382832143389264</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.497673088909225</v>
       </c>
       <c r="E13">
-        <v>-20.80640648355162</v>
+        <v>-21.56743465443665</v>
       </c>
       <c r="F13">
-        <v>1.735090759349712</v>
+        <v>1.388874603349658</v>
       </c>
       <c r="G13">
-        <v>-9.979941938445402</v>
+        <v>-8.491656396356186</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.870416341473221</v>
       </c>
       <c r="E14">
-        <v>-21.72916457514659</v>
+        <v>-22.25943076754876</v>
       </c>
       <c r="F14">
-        <v>1.685842660518475</v>
+        <v>1.524720230469555</v>
       </c>
       <c r="G14">
-        <v>-9.811392133404487</v>
+        <v>-7.419393870005023</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.286652986291641</v>
       </c>
       <c r="E15">
-        <v>-23.04088235620839</v>
+        <v>-23.0955002812149</v>
       </c>
       <c r="F15">
-        <v>2.120220302463674</v>
+        <v>1.789489646691555</v>
       </c>
       <c r="G15">
-        <v>-8.997914951858153</v>
+        <v>-7.46251372565403</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.757772149014146</v>
       </c>
       <c r="E16">
-        <v>-22.91526701570962</v>
+        <v>-23.10363342053268</v>
       </c>
       <c r="F16">
-        <v>2.093323212894775</v>
+        <v>1.848646676395079</v>
       </c>
       <c r="G16">
-        <v>-8.986089683191876</v>
+        <v>-6.641094545358984</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.300314229298768</v>
       </c>
       <c r="E17">
-        <v>-24.83721931167504</v>
+        <v>-24.64061108415802</v>
       </c>
       <c r="F17">
-        <v>2.466453025811784</v>
+        <v>2.136340332122153</v>
       </c>
       <c r="G17">
-        <v>-8.883654783115748</v>
+        <v>-6.346707593824833</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.9150597573869838</v>
       </c>
       <c r="E18">
-        <v>-23.7615754091071</v>
+        <v>-25.07685257073893</v>
       </c>
       <c r="F18">
-        <v>2.143242289322278</v>
+        <v>3.047986823394704</v>
       </c>
       <c r="G18">
-        <v>-8.7127081431044</v>
+        <v>-5.781713339365116</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.598458350321795</v>
       </c>
       <c r="E19">
-        <v>-25.02747409015929</v>
+        <v>-26.46145614095418</v>
       </c>
       <c r="F19">
-        <v>2.69547673186818</v>
+        <v>2.587944702575971</v>
       </c>
       <c r="G19">
-        <v>-8.287875765686348</v>
+        <v>-5.753639913192097</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.3438748125903829</v>
       </c>
       <c r="E20">
-        <v>-25.7873067439063</v>
+        <v>-26.57720393659023</v>
       </c>
       <c r="F20">
-        <v>3.148903510608156</v>
+        <v>2.831703407993364</v>
       </c>
       <c r="G20">
-        <v>-7.577042048585117</v>
+        <v>-5.766051148418824</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.13392724787387</v>
       </c>
       <c r="E21">
-        <v>-25.90899589744042</v>
+        <v>-26.84062979809043</v>
       </c>
       <c r="F21">
-        <v>2.806449799351618</v>
+        <v>2.974412887412857</v>
       </c>
       <c r="G21">
-        <v>-7.196945073039235</v>
+        <v>-5.812233258691657</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.04672101718650006</v>
       </c>
       <c r="E22">
-        <v>-26.37814580463506</v>
+        <v>-27.90510648375544</v>
       </c>
       <c r="F22">
-        <v>3.026608317463254</v>
+        <v>3.168625281734007</v>
       </c>
       <c r="G22">
-        <v>-7.005552503777349</v>
+        <v>-5.236377104317592</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.2121133884964194</v>
       </c>
       <c r="E23">
-        <v>-26.77523863341967</v>
+        <v>-27.69960433328736</v>
       </c>
       <c r="F23">
-        <v>3.094681893890512</v>
+        <v>2.863169772156106</v>
       </c>
       <c r="G23">
-        <v>-7.21231924652361</v>
+        <v>-4.791112039831156</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.3754400146099282</v>
       </c>
       <c r="E24">
-        <v>-27.47105225012024</v>
+        <v>-28.01102749079485</v>
       </c>
       <c r="F24">
-        <v>3.409980064948477</v>
+        <v>3.464395519638376</v>
       </c>
       <c r="G24">
-        <v>-7.430729177931488</v>
+        <v>-3.949531637201949</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.5408821088687075</v>
       </c>
       <c r="E25">
-        <v>-27.0117110176262</v>
+        <v>-28.75299078610759</v>
       </c>
       <c r="F25">
-        <v>3.05328506130301</v>
+        <v>3.254558459365622</v>
       </c>
       <c r="G25">
-        <v>-7.213736160014419</v>
+        <v>-4.707898167156036</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.7071727374671253</v>
       </c>
       <c r="E26">
-        <v>-27.88408530741184</v>
+        <v>-28.5680886639004</v>
       </c>
       <c r="F26">
-        <v>3.602833936729035</v>
+        <v>3.281021484415455</v>
       </c>
       <c r="G26">
-        <v>-7.110675566831366</v>
+        <v>-5.137742710520546</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.8686847677526556</v>
       </c>
       <c r="E27">
-        <v>-27.66043303312101</v>
+        <v>-28.24406276322957</v>
       </c>
       <c r="F27">
-        <v>3.405276594835381</v>
+        <v>3.120063071112289</v>
       </c>
       <c r="G27">
-        <v>-7.126046429770203</v>
+        <v>-4.273130842574629</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.014106440094948</v>
       </c>
       <c r="E28">
-        <v>-27.22667767877032</v>
+        <v>-28.90562753101013</v>
       </c>
       <c r="F28">
-        <v>3.614575216296315</v>
+        <v>3.478058611580151</v>
       </c>
       <c r="G28">
-        <v>-6.754047048613378</v>
+        <v>-4.899734349520183</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.130652612850804</v>
       </c>
       <c r="E29">
-        <v>-26.84651228582639</v>
+        <v>-29.17044363403068</v>
       </c>
       <c r="F29">
-        <v>3.318362630198851</v>
+        <v>3.414587444442847</v>
       </c>
       <c r="G29">
-        <v>-7.079215452571673</v>
+        <v>-4.827345960758479</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.206087851966179</v>
       </c>
       <c r="E30">
-        <v>-26.81009882633071</v>
+        <v>-29.28278601721296</v>
       </c>
       <c r="F30">
-        <v>3.436681659810316</v>
+        <v>3.755730678468157</v>
       </c>
       <c r="G30">
-        <v>-6.38933417818849</v>
+        <v>-5.04769256130683</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.228827023253818</v>
       </c>
       <c r="E31">
-        <v>-26.40295278524908</v>
+        <v>-27.15627349337306</v>
       </c>
       <c r="F31">
-        <v>3.369279060979326</v>
+        <v>3.3431142481945</v>
       </c>
       <c r="G31">
-        <v>-6.794134444548413</v>
+        <v>-5.199173193547262</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.188085866873468</v>
       </c>
       <c r="E32">
-        <v>-26.53509365679291</v>
+        <v>-28.08665753519695</v>
       </c>
       <c r="F32">
-        <v>2.946468741446819</v>
+        <v>3.395750369703187</v>
       </c>
       <c r="G32">
-        <v>-6.30993074342907</v>
+        <v>-4.896682026532975</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.07732217112589</v>
       </c>
       <c r="E33">
-        <v>-26.46489778120001</v>
+        <v>-27.21051102656293</v>
       </c>
       <c r="F33">
-        <v>2.821169888099366</v>
+        <v>3.193244360945208</v>
       </c>
       <c r="G33">
-        <v>-6.129029292981135</v>
+        <v>-4.981299570516747</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.8932063966746203</v>
       </c>
       <c r="E34">
-        <v>-25.38085808782185</v>
+        <v>-27.85197842669745</v>
       </c>
       <c r="F34">
-        <v>3.250250948871065</v>
+        <v>3.085200400598069</v>
       </c>
       <c r="G34">
-        <v>-6.94068898502641</v>
+        <v>-5.874276192643139</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.6348059092751135</v>
       </c>
       <c r="E35">
-        <v>-24.45197749936851</v>
+        <v>-26.21739403431078</v>
       </c>
       <c r="F35">
-        <v>3.384615455074756</v>
+        <v>3.351951271647566</v>
       </c>
       <c r="G35">
-        <v>-7.955020274985865</v>
+        <v>-5.381888822950717</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.3085397351077752</v>
       </c>
       <c r="E36">
-        <v>-25.47923012869048</v>
+        <v>-26.03905819941472</v>
       </c>
       <c r="F36">
-        <v>3.460039963834456</v>
+        <v>3.438124675825993</v>
       </c>
       <c r="G36">
-        <v>-7.622714334844902</v>
+        <v>-5.871786662397607</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.07596260413889673</v>
       </c>
       <c r="E37">
-        <v>-24.58491085386367</v>
+        <v>-25.69339977840924</v>
       </c>
       <c r="F37">
-        <v>3.40502477114493</v>
+        <v>3.796653684901258</v>
       </c>
       <c r="G37">
-        <v>-7.523328447210441</v>
+        <v>-6.044239600629322</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.5072753179153607</v>
       </c>
       <c r="E38">
-        <v>-23.91895346629567</v>
+        <v>-24.66615620603529</v>
       </c>
       <c r="F38">
-        <v>3.859049631149728</v>
+        <v>3.322772858251356</v>
       </c>
       <c r="G38">
-        <v>-7.311397253422918</v>
+        <v>-5.531068626041355</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.9672953911239799</v>
       </c>
       <c r="E39">
-        <v>-23.86031878484436</v>
+        <v>-25.32071089605198</v>
       </c>
       <c r="F39">
-        <v>3.518650271052133</v>
+        <v>3.656127781955544</v>
       </c>
       <c r="G39">
-        <v>-6.950382262365395</v>
+        <v>-5.100876475395222</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.438481983607313</v>
       </c>
       <c r="E40">
-        <v>-22.23618611046739</v>
+        <v>-24.42854717485282</v>
       </c>
       <c r="F40">
-        <v>3.616432416013392</v>
+        <v>3.517654573433968</v>
       </c>
       <c r="G40">
-        <v>-7.988307810383237</v>
+        <v>-6.741857619937782</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.90429996063582</v>
       </c>
       <c r="E41">
-        <v>-22.70119699241903</v>
+        <v>-23.95182565911735</v>
       </c>
       <c r="F41">
-        <v>3.506155177148305</v>
+        <v>3.278861102228954</v>
       </c>
       <c r="G41">
-        <v>-7.487975131396564</v>
+        <v>-5.763879430545062</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.344900030523045</v>
       </c>
       <c r="E42">
-        <v>-20.55437879112873</v>
+        <v>-22.78303557468564</v>
       </c>
       <c r="F42">
-        <v>3.027211368932492</v>
+        <v>3.553300879511236</v>
       </c>
       <c r="G42">
-        <v>-7.920590601377445</v>
+        <v>-6.94613814298405</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.747737714467966</v>
       </c>
       <c r="E43">
-        <v>-21.50103364006218</v>
+        <v>-21.94220210636344</v>
       </c>
       <c r="F43">
-        <v>3.802019848936593</v>
+        <v>3.636861612901233</v>
       </c>
       <c r="G43">
-        <v>-8.309232094960185</v>
+        <v>-5.582673409907515</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.104597769163814</v>
       </c>
       <c r="E44">
-        <v>-20.25056346995413</v>
+        <v>-21.93038278920342</v>
       </c>
       <c r="F44">
-        <v>3.317741354646752</v>
+        <v>3.55986817628063</v>
       </c>
       <c r="G44">
-        <v>-7.984563583378321</v>
+        <v>-6.264218730622813</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.406816172586224</v>
       </c>
       <c r="E45">
-        <v>-19.89693493469515</v>
+        <v>-21.16161545623928</v>
       </c>
       <c r="F45">
-        <v>3.401991289715878</v>
+        <v>3.544069553174438</v>
       </c>
       <c r="G45">
-        <v>-7.939765281140904</v>
+        <v>-6.429931398136572</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.65700425739364</v>
       </c>
       <c r="E46">
-        <v>-21.39907051930548</v>
+        <v>-20.71471847031832</v>
       </c>
       <c r="F46">
-        <v>3.185363273474974</v>
+        <v>3.387675444260697</v>
       </c>
       <c r="G46">
-        <v>-8.025882502253966</v>
+        <v>-5.688687009711596</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.860466161421293</v>
       </c>
       <c r="E47">
-        <v>-20.27320131151847</v>
+        <v>-21.10859608255747</v>
       </c>
       <c r="F47">
-        <v>3.125545206584016</v>
+        <v>3.427602753075633</v>
       </c>
       <c r="G47">
-        <v>-7.719233290042354</v>
+        <v>-6.043716534434116</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.021528994655974</v>
       </c>
       <c r="E48">
-        <v>-18.89852415632804</v>
+        <v>-19.89027354942987</v>
       </c>
       <c r="F48">
-        <v>3.123986219131947</v>
+        <v>3.465722564217661</v>
       </c>
       <c r="G48">
-        <v>-7.602268405594363</v>
+        <v>-6.128148687867689</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.154473162659294</v>
       </c>
       <c r="E49">
-        <v>-18.2831407664777</v>
+        <v>-19.85762778030857</v>
       </c>
       <c r="F49">
-        <v>3.101925138460591</v>
+        <v>3.694966616003202</v>
       </c>
       <c r="G49">
-        <v>-8.027163683377664</v>
+        <v>-6.181547787416133</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.270871447187433</v>
       </c>
       <c r="E50">
-        <v>-18.19941381054988</v>
+        <v>-19.12705359712512</v>
       </c>
       <c r="F50">
-        <v>3.275249420352748</v>
+        <v>3.468335235006091</v>
       </c>
       <c r="G50">
-        <v>-9.262871153548183</v>
+        <v>-5.799441310727913</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.379542646847192</v>
       </c>
       <c r="E51">
-        <v>-17.17340651158002</v>
+        <v>-18.59901541393473</v>
       </c>
       <c r="F51">
-        <v>3.089719973147743</v>
+        <v>3.63132149171131</v>
       </c>
       <c r="G51">
-        <v>-8.062176013000995</v>
+        <v>-6.31960415749482</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.496303077226082</v>
       </c>
       <c r="E52">
-        <v>-17.10285741501453</v>
+        <v>-18.19355396518395</v>
       </c>
       <c r="F52">
-        <v>3.03664978711999</v>
+        <v>3.267355079004069</v>
       </c>
       <c r="G52">
-        <v>-9.061325141117353</v>
+        <v>-6.581080975823077</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.629155164041458</v>
       </c>
       <c r="E53">
-        <v>-16.55657853852123</v>
+        <v>-17.95320520722685</v>
       </c>
       <c r="F53">
-        <v>2.978075928068037</v>
+        <v>3.438280408897719</v>
       </c>
       <c r="G53">
-        <v>-8.098790646665334</v>
+        <v>-5.423207741826361</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.784172198515282</v>
       </c>
       <c r="E54">
-        <v>-16.03874300727012</v>
+        <v>-17.02442424520168</v>
       </c>
       <c r="F54">
-        <v>3.110324783924978</v>
+        <v>3.674833974645562</v>
       </c>
       <c r="G54">
-        <v>-8.059666619482227</v>
+        <v>-6.706765837221507</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.971787272302616</v>
       </c>
       <c r="E55">
-        <v>-16.85430759062953</v>
+        <v>-17.47422398296155</v>
       </c>
       <c r="F55">
-        <v>2.988211831608691</v>
+        <v>3.340156976566506</v>
       </c>
       <c r="G55">
-        <v>-8.073226614011082</v>
+        <v>-6.700919413799154</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.190853077212834</v>
       </c>
       <c r="E56">
-        <v>-15.92332126176262</v>
+        <v>-16.64223462437632</v>
       </c>
       <c r="F56">
-        <v>2.718502032196395</v>
+        <v>3.431501050073208</v>
       </c>
       <c r="G56">
-        <v>-9.255333041355263</v>
+        <v>-6.632444089864869</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.441729670237164</v>
       </c>
       <c r="E57">
-        <v>-15.1505552862497</v>
+        <v>-16.05500475743166</v>
       </c>
       <c r="F57">
-        <v>2.707095413059846</v>
+        <v>3.087528112999935</v>
       </c>
       <c r="G57">
-        <v>-8.908344831747632</v>
+        <v>-6.758142193445456</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.726873141862286</v>
       </c>
       <c r="E58">
-        <v>-15.21350560343033</v>
+        <v>-14.92183112107029</v>
       </c>
       <c r="F58">
-        <v>2.91774924359176</v>
+        <v>2.88592833818062</v>
       </c>
       <c r="G58">
-        <v>-8.782259394338949</v>
+        <v>-6.982054251539602</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.035853976890952</v>
       </c>
       <c r="E59">
-        <v>-15.1611202161096</v>
+        <v>-15.09841443652539</v>
       </c>
       <c r="F59">
-        <v>2.693622845620715</v>
+        <v>3.599258703018553</v>
       </c>
       <c r="G59">
-        <v>-9.045341827253752</v>
+        <v>-7.245328696095683</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.364069513934472</v>
       </c>
       <c r="E60">
-        <v>-14.48416316517696</v>
+        <v>-14.81211072433844</v>
       </c>
       <c r="F60">
-        <v>3.261380893295079</v>
+        <v>3.530366699597329</v>
       </c>
       <c r="G60">
-        <v>-9.136352034673857</v>
+        <v>-6.962949093232469</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.706332219919407</v>
       </c>
       <c r="E61">
-        <v>-15.75509298085167</v>
+        <v>-14.76253299090247</v>
       </c>
       <c r="F61">
-        <v>2.741694662739976</v>
+        <v>3.239039824441576</v>
       </c>
       <c r="G61">
-        <v>-9.164809484129432</v>
+        <v>-7.498227890931688</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.044951744627626</v>
       </c>
       <c r="E62">
-        <v>-15.43089499816854</v>
+        <v>-14.27559070933168</v>
       </c>
       <c r="F62">
-        <v>2.387842616020917</v>
+        <v>3.393243729942315</v>
       </c>
       <c r="G62">
-        <v>-9.302024975641144</v>
+        <v>-7.482115465792055</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.373667982872518</v>
       </c>
       <c r="E63">
-        <v>-13.81649401443406</v>
+        <v>-15.93329749000152</v>
       </c>
       <c r="F63">
-        <v>2.531213132627844</v>
+        <v>3.552119627594844</v>
       </c>
       <c r="G63">
-        <v>-9.353950882424613</v>
+        <v>-7.938527137109216</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.683445607401388</v>
       </c>
       <c r="E64">
-        <v>-14.01617707580229</v>
+        <v>-14.14938213873791</v>
       </c>
       <c r="F64">
-        <v>2.682960100411879</v>
+        <v>2.713720695547436</v>
       </c>
       <c r="G64">
-        <v>-9.279672172159984</v>
+        <v>-8.530028929701878</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.955343857665225</v>
       </c>
       <c r="E65">
-        <v>-13.79887372207022</v>
+        <v>-14.17439290068227</v>
       </c>
       <c r="F65">
-        <v>2.350759920867194</v>
+        <v>3.160374742402124</v>
       </c>
       <c r="G65">
-        <v>-9.204075864770727</v>
+        <v>-7.361985699808521</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.186131063194411</v>
       </c>
       <c r="E66">
-        <v>-13.7968585511368</v>
+        <v>-13.86942734710972</v>
       </c>
       <c r="F66">
-        <v>2.359427957370088</v>
+        <v>2.82844129716114</v>
       </c>
       <c r="G66">
-        <v>-9.132197300022071</v>
+        <v>-7.777194321343913</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.367760690940328</v>
       </c>
       <c r="E67">
-        <v>-14.07695825393324</v>
+        <v>-14.95783701790528</v>
       </c>
       <c r="F67">
-        <v>2.582124593203901</v>
+        <v>2.696177530690948</v>
       </c>
       <c r="G67">
-        <v>-9.314154814497034</v>
+        <v>-7.751958032698049</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.485969848559938</v>
       </c>
       <c r="E68">
-        <v>-13.32363754580926</v>
+        <v>-14.44520923176298</v>
       </c>
       <c r="F68">
-        <v>2.501648700021929</v>
+        <v>2.885383272429578</v>
       </c>
       <c r="G68">
-        <v>-9.041236750785055</v>
+        <v>-7.621568886088314</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.543891510313639</v>
       </c>
       <c r="E69">
-        <v>-14.47476205313704</v>
+        <v>-14.20556238727707</v>
       </c>
       <c r="F69">
-        <v>2.420405738624965</v>
+        <v>2.470304934234802</v>
       </c>
       <c r="G69">
-        <v>-8.231735534431387</v>
+        <v>-8.312115580124891</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.537901370717316</v>
       </c>
       <c r="E70">
-        <v>-14.50221366257154</v>
+        <v>-14.06620765663903</v>
       </c>
       <c r="F70">
-        <v>2.326667683324173</v>
+        <v>2.814216572120267</v>
       </c>
       <c r="G70">
-        <v>-8.755523428563796</v>
+        <v>-7.682333949461637</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.463111725533594</v>
       </c>
       <c r="E71">
-        <v>-14.23365251154665</v>
+        <v>-14.42009884339045</v>
       </c>
       <c r="F71">
-        <v>2.689128124093124</v>
+        <v>2.418750660554172</v>
       </c>
       <c r="G71">
-        <v>-8.383136713578876</v>
+        <v>-7.632281811453396</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.329090407763958</v>
       </c>
       <c r="E72">
-        <v>-13.12603305401056</v>
+        <v>-14.97085638067733</v>
       </c>
       <c r="F72">
-        <v>2.437011191581484</v>
+        <v>2.630829283018901</v>
       </c>
       <c r="G72">
-        <v>-8.411392219756555</v>
+        <v>-7.669313573855683</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.137273006816617</v>
       </c>
       <c r="E73">
-        <v>-14.82857625583033</v>
+        <v>-14.78769319248909</v>
       </c>
       <c r="F73">
-        <v>2.198149794249441</v>
+        <v>2.046157629714176</v>
       </c>
       <c r="G73">
-        <v>-7.861861523510774</v>
+        <v>-7.707457679559166</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.891220524157116</v>
       </c>
       <c r="E74">
-        <v>-15.17366408911085</v>
+        <v>-14.97395838537258</v>
       </c>
       <c r="F74">
-        <v>2.481095248023668</v>
+        <v>2.268577590835455</v>
       </c>
       <c r="G74">
-        <v>-8.044020981263632</v>
+        <v>-7.750713267575283</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.603759637786738</v>
       </c>
       <c r="E75">
-        <v>-14.84094804681929</v>
+        <v>-14.02103612841252</v>
       </c>
       <c r="F75">
-        <v>2.156774499214411</v>
+        <v>2.107335875880531</v>
       </c>
       <c r="G75">
-        <v>-7.437469448649443</v>
+        <v>-7.275845304876685</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.278077338932481</v>
       </c>
       <c r="E76">
-        <v>-15.30803296986644</v>
+        <v>-15.19261122435894</v>
       </c>
       <c r="F76">
-        <v>2.030561128254267</v>
+        <v>1.95424695290396</v>
       </c>
       <c r="G76">
-        <v>-7.447103136168723</v>
+        <v>-7.188969968835131</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.92245674399495</v>
       </c>
       <c r="E77">
-        <v>-14.77753129681587</v>
+        <v>-15.51896928914372</v>
       </c>
       <c r="F77">
-        <v>2.342211169270303</v>
+        <v>2.300902143627497</v>
       </c>
       <c r="G77">
-        <v>-7.224028646096012</v>
+        <v>-7.365160512980682</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.5492776445627</v>
       </c>
       <c r="E78">
-        <v>-15.98475001167667</v>
+        <v>-15.95310503531107</v>
       </c>
       <c r="F78">
-        <v>2.027668469283691</v>
+        <v>2.028858004874111</v>
       </c>
       <c r="G78">
-        <v>-6.613779234114458</v>
+        <v>-6.557321190487727</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.161009043581021</v>
       </c>
       <c r="E79">
-        <v>-17.39822713216482</v>
+        <v>-16.32466632764042</v>
       </c>
       <c r="F79">
-        <v>1.779047247211865</v>
+        <v>1.667322022126684</v>
       </c>
       <c r="G79">
-        <v>-6.456011875894951</v>
+        <v>-6.187079709012256</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.768247054290939</v>
       </c>
       <c r="E80">
-        <v>-18.13509589421894</v>
+        <v>-17.67308286206038</v>
       </c>
       <c r="F80">
-        <v>2.036237101698249</v>
+        <v>2.09462374971717</v>
       </c>
       <c r="G80">
-        <v>-6.699082061024859</v>
+        <v>-5.994902540457563</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.380974213251768</v>
       </c>
       <c r="E81">
-        <v>-17.62252697823875</v>
+        <v>-18.1088624442925</v>
       </c>
       <c r="F81">
-        <v>1.862636145093557</v>
+        <v>2.089774486941181</v>
       </c>
       <c r="G81">
-        <v>-6.507941093223958</v>
+        <v>-4.836602246086281</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.999821882268759</v>
       </c>
       <c r="E82">
-        <v>-18.71186498620587</v>
+        <v>-18.9936719237032</v>
       </c>
       <c r="F82">
-        <v>1.830213844947984</v>
+        <v>2.060635835180306</v>
       </c>
       <c r="G82">
-        <v>-5.85001651493136</v>
+        <v>-4.980279922490651</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.635402160392887</v>
       </c>
       <c r="E83">
-        <v>-19.98270423240043</v>
+        <v>-19.2166630407889</v>
       </c>
       <c r="F83">
-        <v>2.368380952259545</v>
+        <v>1.832453750405154</v>
       </c>
       <c r="G83">
-        <v>-5.129916580865709</v>
+        <v>-5.473170495105042</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.294749460104378</v>
       </c>
       <c r="E84">
-        <v>-20.67289348438348</v>
+        <v>-20.39321945814376</v>
       </c>
       <c r="F84">
-        <v>2.074726364701926</v>
+        <v>1.826194606309601</v>
       </c>
       <c r="G84">
-        <v>-4.825041821063147</v>
+        <v>-4.543062794210184</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.976639829070334</v>
       </c>
       <c r="E85">
-        <v>-21.25649151517398</v>
+        <v>-21.35721836252659</v>
       </c>
       <c r="F85">
-        <v>1.802445312871339</v>
+        <v>1.804554336278867</v>
       </c>
       <c r="G85">
-        <v>-4.274587482611908</v>
+        <v>-4.460266050273011</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.691164371652532</v>
       </c>
       <c r="E86">
-        <v>-22.37962552466035</v>
+        <v>-23.09293716492656</v>
       </c>
       <c r="F86">
-        <v>2.209049452535476</v>
+        <v>1.970221189899546</v>
       </c>
       <c r="G86">
-        <v>-4.598736238544108</v>
+        <v>-4.082873790432714</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.442585147633852</v>
       </c>
       <c r="E87">
-        <v>-24.0878791322038</v>
+        <v>-23.14464780962015</v>
       </c>
       <c r="F87">
-        <v>1.796512545532489</v>
+        <v>2.138674671463242</v>
       </c>
       <c r="G87">
-        <v>-4.434688775436602</v>
+        <v>-3.699224599523194</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.227706562862308</v>
       </c>
       <c r="E88">
-        <v>-25.48649380099878</v>
+        <v>-25.2208308733388</v>
       </c>
       <c r="F88">
-        <v>1.94870186150962</v>
+        <v>1.68744472307549</v>
       </c>
       <c r="G88">
-        <v>-4.463473968900566</v>
+        <v>-3.313363964193441</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.055680903932372</v>
       </c>
       <c r="E89">
-        <v>-26.33979415826411</v>
+        <v>-27.15973324751493</v>
       </c>
       <c r="F89">
-        <v>2.05677564308326</v>
+        <v>1.70998625684047</v>
       </c>
       <c r="G89">
-        <v>-3.938974307477213</v>
+        <v>-3.465678853909769</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.928794334893478</v>
       </c>
       <c r="E90">
-        <v>-28.37790634100027</v>
+        <v>-27.4802405238818</v>
       </c>
       <c r="F90">
-        <v>1.738821726131921</v>
+        <v>1.775046232656343</v>
       </c>
       <c r="G90">
-        <v>-3.362608329090099</v>
+        <v>-2.434490266064344</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.843984360493546</v>
       </c>
       <c r="E91">
-        <v>-29.84927773743949</v>
+        <v>-29.15981983400868</v>
       </c>
       <c r="F91">
-        <v>1.673867781343606</v>
+        <v>1.300381770443393</v>
       </c>
       <c r="G91">
-        <v>-3.593962493556527</v>
+        <v>-3.046514130454947</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.809651697893545</v>
       </c>
       <c r="E92">
-        <v>-31.16449376467221</v>
+        <v>-32.80535915050752</v>
       </c>
       <c r="F92">
-        <v>1.449820906643229</v>
+        <v>1.745377425757676</v>
       </c>
       <c r="G92">
-        <v>-3.758132446848986</v>
+        <v>-2.767392104402376</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.827368905536985</v>
       </c>
       <c r="E93">
-        <v>-33.46770734429141</v>
+        <v>-33.44605897429774</v>
       </c>
       <c r="F93">
-        <v>1.75906702545634</v>
+        <v>1.345653705741191</v>
       </c>
       <c r="G93">
-        <v>-3.890372188415173</v>
+        <v>-3.571672590440615</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.893267160543529</v>
       </c>
       <c r="E94">
-        <v>-35.31494434760427</v>
+        <v>-36.31950026519979</v>
       </c>
       <c r="F94">
-        <v>1.884031218373063</v>
+        <v>1.110693918876334</v>
       </c>
       <c r="G94">
-        <v>-4.090802546999268</v>
+        <v>-3.241806522362094</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.012236093342144</v>
       </c>
       <c r="E95">
-        <v>-37.45980624812325</v>
+        <v>-37.71578276988082</v>
       </c>
       <c r="F95">
-        <v>1.501332105218913</v>
+        <v>0.9028863587404385</v>
       </c>
       <c r="G95">
-        <v>-3.348780180372564</v>
+        <v>-2.853986044073092</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.184355153741655</v>
       </c>
       <c r="E96">
-        <v>-40.38158220634617</v>
+        <v>-40.34698692916458</v>
       </c>
       <c r="F96">
-        <v>1.188340109010343</v>
+        <v>1.157871099200571</v>
       </c>
       <c r="G96">
-        <v>-4.09179240011551</v>
+        <v>-3.688733480709244</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.397337694823261</v>
       </c>
       <c r="E97">
-        <v>-41.50692837538529</v>
+        <v>-41.99068034701767</v>
       </c>
       <c r="F97">
-        <v>1.46507777746799</v>
+        <v>0.7676371561505577</v>
       </c>
       <c r="G97">
-        <v>-4.643892079699766</v>
+        <v>-2.851582588011581</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.659639380118718</v>
       </c>
       <c r="E98">
-        <v>-44.86851425770717</v>
+        <v>-44.23995527273151</v>
       </c>
       <c r="F98">
-        <v>1.243250927407116</v>
+        <v>0.5664615054414753</v>
       </c>
       <c r="G98">
-        <v>-4.112758085015715</v>
+        <v>-4.367782650087932</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.949810260381221</v>
       </c>
       <c r="E99">
-        <v>-46.25649154105813</v>
+        <v>-46.81736116080413</v>
       </c>
       <c r="F99">
-        <v>1.021033087932121</v>
+        <v>0.5230475982281561</v>
       </c>
       <c r="G99">
-        <v>-4.578634606029653</v>
+        <v>-4.227286407946802</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.280028603379288</v>
       </c>
       <c r="E100">
-        <v>-49.03984337005159</v>
+        <v>-49.04262611732931</v>
       </c>
       <c r="F100">
-        <v>0.4726886587097657</v>
+        <v>0.2658651990483964</v>
       </c>
       <c r="G100">
-        <v>-4.708715871904236</v>
+        <v>-4.994204077028826</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.612977198635229</v>
       </c>
       <c r="E101">
-        <v>-50.44019584074702</v>
+        <v>-50.27196755983607</v>
       </c>
       <c r="F101">
-        <v>0.2810624274201561</v>
+        <v>0.02264327570801673</v>
       </c>
       <c r="G101">
-        <v>-4.7437646175285</v>
+        <v>-4.146217768781129</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.998094000768767</v>
       </c>
       <c r="E102">
-        <v>-52.582105176213</v>
+        <v>-53.25811464395952</v>
       </c>
       <c r="F102">
-        <v>0.1823823321942622</v>
+        <v>-0.0796791509879866</v>
       </c>
       <c r="G102">
-        <v>-5.955056814346895</v>
+        <v>-4.608674496252999</v>
       </c>
     </row>
   </sheetData>
